--- a/docs/harness/wirelist/ClusterLED-wirelist.xlsx
+++ b/docs/harness/wirelist/ClusterLED-wirelist.xlsx
@@ -1601,12 +1601,12 @@
       </c>
       <c r="AE6" s="54" t="inlineStr">
         <is>
-          <t>flying lead FL_CL_C12_C9: EWD C12 pin 9 B-O</t>
+          <t>flying lead FL_CL_C12_C9: EWD C12 pin 9 B-O; splice sp_led_12v: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF6" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_led_12v is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG6" s="54" t="inlineStr"/>
@@ -1835,10 +1835,14 @@
       <c r="AB8" s="53" t="inlineStr"/>
       <c r="AC8" s="54" t="inlineStr"/>
       <c r="AD8" s="54" t="inlineStr"/>
-      <c r="AE8" s="54" t="inlineStr"/>
+      <c r="AE8" s="54" t="inlineStr">
+        <is>
+          <t>splice sp_led_gnd: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF8" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_led_gnd is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG8" s="54" t="inlineStr"/>
@@ -2184,10 +2188,14 @@
       <c r="AB11" s="37" t="inlineStr"/>
       <c r="AC11" s="38" t="inlineStr"/>
       <c r="AD11" s="38" t="inlineStr"/>
-      <c r="AE11" s="38" t="inlineStr"/>
+      <c r="AE11" s="38" t="inlineStr">
+        <is>
+          <t>splice sp_led_gnd: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF11" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_led_gnd is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG11" s="38" t="inlineStr"/>
@@ -2291,10 +2299,14 @@
       <c r="AB12" s="53" t="inlineStr"/>
       <c r="AC12" s="54" t="inlineStr"/>
       <c r="AD12" s="54" t="inlineStr"/>
-      <c r="AE12" s="54" t="inlineStr"/>
+      <c r="AE12" s="54" t="inlineStr">
+        <is>
+          <t>splice sp_led_gnd: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF12" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_led_gnd is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG12" s="54" t="inlineStr"/>
@@ -2402,10 +2414,14 @@
       <c r="AB13" s="37" t="inlineStr"/>
       <c r="AC13" s="38" t="inlineStr"/>
       <c r="AD13" s="38" t="inlineStr"/>
-      <c r="AE13" s="38" t="inlineStr"/>
+      <c r="AE13" s="38" t="inlineStr">
+        <is>
+          <t>splice sp_led_12v: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF13" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_led_12v is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG13" s="38" t="inlineStr"/>
@@ -2509,10 +2525,14 @@
       <c r="AB14" s="53" t="inlineStr"/>
       <c r="AC14" s="54" t="inlineStr"/>
       <c r="AD14" s="54" t="inlineStr"/>
-      <c r="AE14" s="54" t="inlineStr"/>
+      <c r="AE14" s="54" t="inlineStr">
+        <is>
+          <t>splice sp_led_12v: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF14" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_led_12v is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG14" s="54" t="inlineStr"/>
@@ -2616,10 +2636,14 @@
       <c r="AB15" s="37" t="inlineStr"/>
       <c r="AC15" s="38" t="inlineStr"/>
       <c r="AD15" s="38" t="inlineStr"/>
-      <c r="AE15" s="38" t="inlineStr"/>
+      <c r="AE15" s="38" t="inlineStr">
+        <is>
+          <t>splice sp_led_12v: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF15" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_led_12v is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG15" s="38" t="inlineStr"/>
@@ -2721,10 +2745,14 @@
       <c r="AB16" s="53" t="inlineStr"/>
       <c r="AC16" s="54" t="inlineStr"/>
       <c r="AD16" s="54" t="inlineStr"/>
-      <c r="AE16" s="54" t="inlineStr"/>
+      <c r="AE16" s="54" t="inlineStr">
+        <is>
+          <t>splice sp_led_gnd: node of the wire list (SoT); end t_led_gnd: end row of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF16" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_led_gnd is not named in the SoT (drawing only); end t_led_gnd (Ground stud, LH kick panel (EWD ground point ID)) is drawing-only: not named in the SoT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG16" s="54" t="inlineStr"/>
@@ -2935,7 +2963,7 @@
       </c>
       <c r="L3" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: not named in the SoT (drawing only)</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -2991,7 +3019,7 @@
       </c>
       <c r="L4" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: not named in the SoT (drawing only)</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>

--- a/docs/harness/wirelist/ClusterLED-wirelist.xlsx
+++ b/docs/harness/wirelist/ClusterLED-wirelist.xlsx
@@ -1187,7 +1187,7 @@
       </c>
       <c r="V3" s="34" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="W3" s="34" t="inlineStr"/>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="V4" s="50" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="W4" s="50" t="inlineStr"/>
@@ -1564,14 +1564,10 @@
       </c>
       <c r="V6" s="50" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="W6" s="50" t="inlineStr">
-        <is>
-          <t>Orange</t>
-        </is>
-      </c>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="W6" s="50" t="inlineStr"/>
       <c r="X6" s="50" t="inlineStr">
         <is>
           <t>Yellow-Yellow</t>
@@ -1693,7 +1689,7 @@
       </c>
       <c r="V7" s="34" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W7" s="34" t="inlineStr"/>
@@ -2042,14 +2038,10 @@
       </c>
       <c r="V10" s="50" t="inlineStr">
         <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="W10" s="50" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="W10" s="50" t="inlineStr"/>
       <c r="X10" s="50" t="inlineStr">
         <is>
           <t>White</t>
@@ -2395,14 +2387,10 @@
       </c>
       <c r="V13" s="34" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="W13" s="34" t="inlineStr">
-        <is>
-          <t>Orange</t>
-        </is>
-      </c>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="W13" s="34" t="inlineStr"/>
       <c r="X13" s="34" t="inlineStr">
         <is>
           <t>Blue</t>
